--- a/sources/标准汉语会话360句1_语法零基础版.xlsx
+++ b/sources/标准汉语会话360句1_语法零基础版.xlsx
@@ -4,9 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet name="01_语法总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_学生练习版" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_按课索引" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_说明与来源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="进阶练习" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_学生练习版" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_按课索引" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_说明与来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -26,8 +27,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B2A1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -346,6 +356,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -3013,6 +3024,1376 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>语法编号</t>
+        </is>
+      </c>
+      <c r="B1" s="68" t="inlineStr">
+        <is>
+          <t>课次</t>
+        </is>
+      </c>
+      <c r="C1" s="68" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="D1" s="68" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="E1" s="68" t="inlineStr">
+        <is>
+          <t>选项A</t>
+        </is>
+      </c>
+      <c r="F1" s="68" t="inlineStr">
+        <is>
+          <t>选项B</t>
+        </is>
+      </c>
+      <c r="G1" s="68" t="inlineStr">
+        <is>
+          <t>选项C</t>
+        </is>
+      </c>
+      <c r="H1" s="68" t="inlineStr">
+        <is>
+          <t>选项D</t>
+        </is>
+      </c>
+      <c r="I1" s="68" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="J1" s="68" t="inlineStr">
+        <is>
+          <t>解析（中文）</t>
+        </is>
+      </c>
+      <c r="K1" s="68" t="inlineStr">
+        <is>
+          <t>解析（英文）</t>
+        </is>
+      </c>
+      <c r="L1" s="68" t="inlineStr">
+        <is>
+          <t>题干（英文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>360-1.1.1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>My mom is a Chinese teacher.</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr"/>
+      <c r="F2" s="14" t="inlineStr"/>
+      <c r="G2" s="14" t="inlineStr"/>
+      <c r="H2" s="14" t="inlineStr"/>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>我妈妈是汉语老师。</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr"/>
+      <c r="K2" s="14" t="inlineStr"/>
+      <c r="L2" s="14" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>360-1.1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>We study Chinese.</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr"/>
+      <c r="F3" s="14" t="inlineStr"/>
+      <c r="G3" s="14" t="inlineStr"/>
+      <c r="H3" s="14" t="inlineStr"/>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>我们学习汉语。</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr"/>
+      <c r="K3" s="14" t="inlineStr"/>
+      <c r="L3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>360-1.1.1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Her name is Mary.</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="14" t="inlineStr"/>
+      <c r="G4" s="14" t="inlineStr"/>
+      <c r="H4" s="14" t="inlineStr"/>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>她叫玛丽。</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr"/>
+      <c r="K4" s="14" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>360-1.2.1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>My younger sister is very pretty.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>我妹妹很好看。</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>360-1.2.1</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>I'm fine. (no 是)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>我很好。</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>360-1.2.2</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Are you David?</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>你是大卫吗？</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr"/>
+      <c r="K7" s="14" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>360-1.2.2</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Is your mom a teacher?</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>你妈妈是老师吗？</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>360-1.3.1</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Who is your Chinese teacher?</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>你的汉语老师是谁？</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>360-1.3.1</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>What day of the week is it today?</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>今天星期几？</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>360-1.3.1</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>What time is it now?</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>现在几点？</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>360-1.3.2</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>What is your older brother's name?</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>你哥哥的名字是什么？</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>360-1.3.2</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Is this your apple?</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>这是你的苹果吗？</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>360-1.4.1</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Today is Wednesday, October 8th.</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>今天十月八号星期三。</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>360-1.4.1</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>What's the date today? (month and day)</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>今天几月几号？</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
+      <c r="L15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>360-1.4.2</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Is tomorrow the 8th? (no 是)</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>明天八号吗？</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>360-1.4.2</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>My dad is fifty years old.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>我爸爸五十岁。</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.1</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>It's a quarter to eleven now.</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>现在差一刻十一点。</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.1</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>It's half past two now.</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>现在两点半。</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.1</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>It's 10:10 now.</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>现在十点十分。</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.2</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>I'll go to the bank at nine tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>我明天早上九点去银行。</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.2</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>I eat breakfast at seven in the morning.</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>我早上七点吃早饭。</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="inlineStr"/>
+      <c r="L22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.3</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>We are eating together tonight.</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>我们今天晚上一起吃饭。</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr"/>
+      <c r="K23" s="14" t="inlineStr"/>
+      <c r="L23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.3</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>My dad goes to work at eight.</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="14" t="inlineStr"/>
+      <c r="H24" s="14" t="inlineStr"/>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>我爸爸八点上班。</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="inlineStr"/>
+      <c r="L24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>360-1.5.3</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>I don't go to work tomorrow.</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>我明天不上班。</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>360-1.6.1</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>How old is your older brother?</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr"/>
+      <c r="G26" s="14" t="inlineStr"/>
+      <c r="H26" s="14" t="inlineStr"/>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>你哥哥多大？</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr"/>
+      <c r="L26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>360-1.6.1</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>How old are you? (asking a small child)</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>你几岁？</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr"/>
+      <c r="K27" s="14" t="inlineStr"/>
+      <c r="L27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>360-1.6.2</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>My older sister doesn't have a boyfriend.</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="14" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>我姐姐没有男朋友。</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="inlineStr"/>
+      <c r="L28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>360-1.6.2</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>I have two younger sisters.</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>我有两个妹妹。</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>360-1.6.3</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>We eat breakfast at home.</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr"/>
+      <c r="G30" s="14" t="inlineStr"/>
+      <c r="H30" s="14" t="inlineStr"/>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>我们在家吃早饭。</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="inlineStr"/>
+      <c r="L30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>360-1.6.3</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>My older sister studies at the library.</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr"/>
+      <c r="G31" s="14" t="inlineStr"/>
+      <c r="H31" s="14" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>我姐姐在图书馆学习。</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr"/>
+      <c r="K31" s="14" t="inlineStr"/>
+      <c r="L31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>360-1.7.1</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>This watermelon is eight yuan.</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr"/>
+      <c r="G32" s="14" t="inlineStr"/>
+      <c r="H32" s="14" t="inlineStr"/>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>这个西瓜八块钱。</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="inlineStr"/>
+      <c r="L32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>360-1.7.1</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Mineral water is 1.5 yuan a bottle.</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr"/>
+      <c r="H33" s="14" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>矿泉水一块五一瓶。</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>360-1.7.2</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>I want two bottles of mineral water.</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr"/>
+      <c r="G34" s="14" t="inlineStr"/>
+      <c r="H34" s="14" t="inlineStr"/>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>我要两瓶矿泉水。</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="inlineStr"/>
+      <c r="L34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>360-1.7.2</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>I have three apples.</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr"/>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>我有三个苹果。</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr"/>
+      <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>360-1.8.1</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>The restroom is to the left of my room.</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr"/>
+      <c r="G36" s="14" t="inlineStr"/>
+      <c r="H36" s="14" t="inlineStr"/>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>洗手间在我房间左边。</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="inlineStr"/>
+      <c r="L36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>360-1.8.1</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>The bank is west of the library.</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>银行在图书馆西边。</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>360-1.8.2</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Turn left at the first intersection.</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="14" t="inlineStr"/>
+      <c r="H38" s="14" t="inlineStr"/>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>在第一个路口往左拐。</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="inlineStr"/>
+      <c r="L38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>360-1.8.2</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Go south from here.</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>从这儿往南走。</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="14" t="inlineStr"/>
+      <c r="L39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>360-1.8.3</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Where is your home?</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="14" t="inlineStr"/>
+      <c r="H40" s="14" t="inlineStr"/>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>你家在哪儿？</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>360-1.8.3</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>My mom isn't at home.</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>我妈妈不在家。</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4660,7 +6041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4895,13 +6276,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5040,6 +6421,18 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>进阶练习（网站，2026-10）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>「进阶练习」表：本册学生是零基础，选择题读不懂，所以网站上的语法练习只保留英译汉（看英文、想中文、再看答案自评）。本表是每个语法点完整的翻译题清单（每点 2–3 道，覆盖本册全部语法点；原有翻译题经核对后保留或修改，不足的已补充），网站只用这里的题，01 表「练习1–3」中的填空/选择/排序等题不再显示。01 表原有练习未改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
